--- a/artfynd/A 30378-2024 artfynd.xlsx
+++ b/artfynd/A 30378-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119136978</v>
+        <v>135293601</v>
       </c>
       <c r="B2" t="n">
-        <v>110078</v>
+        <v>43224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>201028</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bullsta-Sibble, Srm</t>
+          <t>Bullsta, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658198</v>
+        <v>658107</v>
       </c>
       <c r="R2" t="n">
-        <v>6557184</v>
+        <v>6557133</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,21 +769,119 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lennart Didrik</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lennart Didrik</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119136978</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bullsta-Sibble, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>658198</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6557184</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Karin Agstam-Norlin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Karin Agstam-Norlin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>

--- a/artfynd/A 30378-2024 artfynd.xlsx
+++ b/artfynd/A 30378-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293601</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,8 +896,17 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119136978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 30378-2024 artfynd.xlsx
+++ b/artfynd/A 30378-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135293601</v>
       </c>
       <c r="B2" t="n">
-        <v>43224</v>
+        <v>43229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 30378-2024 artfynd.xlsx
+++ b/artfynd/A 30378-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119136978</v>
+        <v>135293601</v>
       </c>
       <c r="B2" t="n">
-        <v>110078</v>
+        <v>43229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>201028</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Mindre tåtelsmygare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymelicus lineola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ochsenheimer, 1808)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bullsta-Sibble, Srm</t>
+          <t>Bullsta, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>658198</v>
+        <v>658107</v>
       </c>
       <c r="R2" t="n">
-        <v>6557184</v>
+        <v>6557133</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,26 +774,129 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Lennart Didrik</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Lennart Didrik</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135293601</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>119136978</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bullsta-Sibble, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>658198</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6557184</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Grödinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Karin Agstam-Norlin</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Karin Agstam-Norlin</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/119136978</t>
         </is>
@@ -787,6 +905,7 @@
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
